--- a/outputs/reports/random_forest_v2/evaluation.xlsx
+++ b/outputs/reports/random_forest_v2/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9987455251965853</v>
+        <v>0.9988870360737998</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8109048723897911</v>
+        <v>0.8385922330097088</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8090277777777778</v>
+        <v>0.8138987043580683</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8099652375434531</v>
+        <v>0.8260609683203826</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9993745203376823</v>
+        <v>0.9994896686683422</v>
       </c>
       <c r="G2" t="n">
-        <v>260437</v>
+        <v>260482</v>
       </c>
       <c r="H2" t="n">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="I2" t="n">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="J2" t="n">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9853408977857366</v>
+        <v>0.9828619207710347</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8783294526351263</v>
+        <v>0.8841702825731377</v>
       </c>
     </row>
   </sheetData>
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003304470213872656</v>
+        <v>0.003247100939326255</v>
       </c>
       <c r="C2" t="n">
         <v>2615</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3108986615678777</v>
+        <v>0.3043977055449331</v>
       </c>
       <c r="E2" t="n">
-        <v>94.08426811132357</v>
+        <v>93.74445427868125</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9409722222222222</v>
+        <v>0.9375736160188457</v>
       </c>
       <c r="G2" t="n">
         <v>13074</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06287287746672786</v>
+        <v>0.06218448829738412</v>
       </c>
       <c r="I2" t="n">
-        <v>19.0266134652321</v>
+        <v>19.15077155263515</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9513888888888888</v>
+        <v>0.9575971731448764</v>
       </c>
       <c r="K2" t="n">
         <v>26147</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03170535816728497</v>
+        <v>0.03113167858645351</v>
       </c>
       <c r="M2" t="n">
-        <v>9.594687231309024</v>
+        <v>9.587530282601273</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9594907407407407</v>
+        <v>0.9587750294464076</v>
       </c>
     </row>
   </sheetData>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>255455</v>
+        <v>255911</v>
       </c>
       <c r="C2" t="n">
         <v>44</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001722416864026932</v>
+        <v>0.0001719347741988426</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4210</v>
+        <v>3880</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003800475059382423</v>
+        <v>0.004381443298969072</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>576</v>
+        <v>529</v>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03645833333333334</v>
+        <v>0.05103969754253308</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="C5" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1557788944723618</v>
+        <v>0.1445086705202312</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="C6" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3291925465838509</v>
+        <v>0.3103448275862069</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C7" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4186046511627907</v>
+        <v>0.4918032786885246</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5748031496062992</v>
+        <v>0.6020408163265306</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C9" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7796610169491526</v>
+        <v>0.776</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9487179487179487</v>
+        <v>0.9691358024691358</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="C11" t="n">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="D11" t="n">
-        <v>0.996996996996997</v>
+        <v>0.9968652037617555</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>

--- a/outputs/reports/random_forest_v2/evaluation.xlsx
+++ b/outputs/reports/random_forest_v2/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9988870360737998</v>
+        <v>0.9959284232365145</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8385922330097088</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8138987043580683</v>
+        <v>0.04938271604938271</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8260609683203826</v>
+        <v>0.09248554913294797</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9994896686683422</v>
+        <v>0.9999218709307777</v>
       </c>
       <c r="G2" t="n">
-        <v>260482</v>
+        <v>38395</v>
       </c>
       <c r="H2" t="n">
-        <v>133</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="J2" t="n">
-        <v>691</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9828619207710347</v>
+        <v>0.8600092661719134</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8841702825731377</v>
+        <v>0.1599838936894722</v>
       </c>
     </row>
   </sheetData>
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.004201244813278008</v>
       </c>
       <c r="C2" t="n">
-        <v>2615</v>
+        <v>386</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3043977055449331</v>
+        <v>0.1424870466321244</v>
       </c>
       <c r="E2" t="n">
-        <v>93.74445427868125</v>
+        <v>33.91543529712787</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9375736160188457</v>
+        <v>0.3395061728395062</v>
       </c>
       <c r="G2" t="n">
-        <v>13074</v>
+        <v>1928</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06218448829738412</v>
+        <v>0.04201244813278009</v>
       </c>
       <c r="I2" t="n">
-        <v>19.15077155263515</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9575971731448764</v>
+        <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>26147</v>
+        <v>3856</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03113167858645351</v>
+        <v>0.02956431535269709</v>
       </c>
       <c r="M2" t="n">
-        <v>9.587530282601273</v>
+        <v>7.037037037037037</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9587750294464076</v>
+        <v>0.7037037037037037</v>
       </c>
     </row>
   </sheetData>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>255911</v>
+        <v>37514</v>
       </c>
       <c r="C2" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001719347741988426</v>
+        <v>0.002452417764034761</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3880</v>
+        <v>874</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004381443298969072</v>
+        <v>0.03775743707093822</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>529</v>
+        <v>137</v>
       </c>
       <c r="C4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05103969754253308</v>
+        <v>0.1605839416058394</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>173</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1445086705202312</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>145</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3103448275862069</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>122</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4918032786885246</v>
+        <v>0.625</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -814,16 +814,12 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
-      </c>
-      <c r="C8" t="n">
-        <v>59</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.6020408163265306</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -833,16 +829,12 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
-      </c>
-      <c r="C9" t="n">
-        <v>97</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.776</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -852,16 +844,12 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>162</v>
-      </c>
-      <c r="C10" t="n">
-        <v>157</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.9691358024691358</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -871,16 +859,12 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>319</v>
-      </c>
-      <c r="C11" t="n">
-        <v>318</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.9968652037617555</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
